--- a/tests/fixtures/jira-sample.xlsx
+++ b/tests/fixtures/jira-sample.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,6 +431,9 @@
       <c r="J1" t="str">
         <v>Resolved</v>
       </c>
+      <c r="K1" t="str">
+        <v>T-Shirt</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -463,6 +466,9 @@
       <c r="J2" t="str">
         <v>2024-01-10</v>
       </c>
+      <c r="K2" t="str">
+        <v>abc</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -495,6 +501,9 @@
       <c r="J3" t="str">
         <v>2024-01-12</v>
       </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -527,6 +536,9 @@
       <c r="J4" t="str">
         <v/>
       </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -559,6 +571,9 @@
       <c r="J5" t="str">
         <v/>
       </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -591,10 +606,83 @@
       <c r="J6" t="str">
         <v/>
       </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PROJ-E1</v>
+      </c>
+      <c r="B7" t="str">
+        <v>User Authentication Epic</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Epic</v>
+      </c>
+      <c r="D7" t="str">
+        <v>In Progress</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>Alice</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2024-01-01</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PROJ-E2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Dashboard Epic</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Epic</v>
+      </c>
+      <c r="D8" t="str">
+        <v>In Progress</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>Bob</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2024-01-01</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K8"/>
   </ignoredErrors>
 </worksheet>
 </file>
